--- a/evaluate-fliter-1.xlsx
+++ b/evaluate-fliter-1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,269 +435,839 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>600026</v>
+        <v>600011</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中远海能</t>
+          <t>华能国际</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.0/37</t>
+          <t>6.0/110</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>600131</v>
+        <v>600012</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>国网信通</t>
+          <t>皖通高速</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.0/134</t>
+          <t>8.0/36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>600158</v>
+        <v>600063</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中体产业</t>
+          <t>皖维高新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.0/2</t>
+          <t>6.0/28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>600502</v>
+        <v>600132</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>安徽建工</t>
+          <t>重庆啤酒</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.0/48</t>
+          <t>6.0/17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>600516</v>
+        <v>600158</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>方大炭素</t>
+          <t>中体产业</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.0/10</t>
+          <t>2.0/2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>600867</v>
+        <v>600251</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>通化东宝</t>
+          <t>冠农股份</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.0/58</t>
+          <t>6.0/28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>601868</v>
+        <v>600256</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中国能建</t>
+          <t>广汇能源</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10.0/48</t>
+          <t>10.0/31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>601872</v>
+        <v>600365</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>ST通葡</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.0/37</t>
+          <t>8.0/18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>601877</v>
+        <v>600389</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>江山股份</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.0/139</t>
+          <t>6.0/63</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>603045</v>
+        <v>600482</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>福达合金</t>
+          <t>中国动力</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.0/34</t>
+          <t>6.0/35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>603165</v>
+        <v>600502</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>荣晟环保</t>
+          <t>安徽建工</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7.0/25</t>
+          <t>10.0/48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>603220</v>
+        <v>600516</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中贝通信</t>
+          <t>方大炭素</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.0/40</t>
+          <t>9.0/10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603477</v>
+        <v>600563</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>巨星农牧</t>
+          <t>法拉电子</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10.0/22</t>
+          <t>7.0/62</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>603489</v>
+        <v>600578</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>八方股份</t>
+          <t>京能电力</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.0/26</t>
+          <t>6.0/110</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>603538</v>
+        <v>600598</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>北大荒</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.0/160</t>
+          <t>9.0/21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>603588</v>
+        <v>600600</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>高能环境</t>
+          <t>青岛啤酒</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.0/109</t>
+          <t>6.0/17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>603688</v>
+        <v>600603</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>石英股份</t>
+          <t>广汇物流</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10.0/12</t>
+          <t>10.0/48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>600623</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>华谊集团</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7.0/63</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>600735</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ST新华锦</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10.0/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>600759</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>洲际油气</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>600803</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>新奥股份</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6.0/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>600938</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中国海油</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>600971</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>恒源煤电</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8.0/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>600985</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>淮北矿业</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>9.0/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>600989</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>宝丰能源</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>6.0/63</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>600997</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>开滦股份</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7.0/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>601001</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>晋控煤业</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10.0/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>601088</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>中国神华</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7.0/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>601101</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>昊华能源</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6.0/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>601117</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>中国化学</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6.0/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>601118</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6.0/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>601139</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>深圳燃气</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>6.0/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>601216</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>君正集团</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>6.0/63</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>601699</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>潞安环能</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>6.0/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>601789</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>8.0/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>601877</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>正泰电器</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>8.0/139</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>601952</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>苏垦农发</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6.0/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>601969</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>海南矿业</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9.0/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>601991</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>大唐发电</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6.0/110</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>603017</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>中衡设计</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10.0/47</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>603055</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>台华新材</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9.0/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>603063</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>禾望电气</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10.0/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>603071</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>物产环能</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6.0/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>603093</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>南华期货</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7.0/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>603220</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>中贝通信</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6.0/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>603393</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>新天然气</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>6.0/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>603477</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>巨星农牧</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10.0/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>603489</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>八方股份</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>6.0/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>603588</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>高能环境</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>8.0/109</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>603628</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>清源股份</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6.0/68</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>603688</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>石英股份</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10.0/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>603826</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>坤彩科技</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10.0/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>603856</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>东宏股份</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6.0/37</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>605117</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>德业股份</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>10.0/68</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>605183</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>确成股份</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>6.0/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>605377</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>华旺科技</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>10.0/25</t>
         </is>
